--- a/Formato convalidacion RPA.xlsx
+++ b/Formato convalidacion RPA.xlsx
@@ -8,15 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/591ae44d10882bc8/Documentos/GitHub/app_2025G_conva/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{3727DEED-5A95-4A46-B413-E8B90488D561}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9FE8CD20-EA36-4EBF-BCC4-D70A9683EC3C}"/>
+  <xr:revisionPtr revIDLastSave="57" documentId="13_ncr:1_{3727DEED-5A95-4A46-B413-E8B90488D561}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{03D90186-35FA-4E88-B1E1-20156065B8E9}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{FF5BE537-666D-40A5-9F6F-D57D02745E6B}"/>
   </bookViews>
   <sheets>
     <sheet name="dataset" sheetId="1" r:id="rId1"/>
+    <sheet name="Hoja1" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">dataset!$A$1:$K$673</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">dataset!$A$1:$L$679</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Hoja1!$B$3:$I$8</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7402" uniqueCount="2077">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7498" uniqueCount="2115">
   <si>
     <t>Nombre</t>
   </si>
@@ -6270,13 +6272,127 @@
   </si>
   <si>
     <t>versión</t>
+  </si>
+  <si>
+    <t>N00254869</t>
+  </si>
+  <si>
+    <t>JULCA/TORRES HELEN DENISSE</t>
+  </si>
+  <si>
+    <t>CONT1212A</t>
+  </si>
+  <si>
+    <t>CONTABILIDAD 2</t>
+  </si>
+  <si>
+    <t>ADM-WVCONT1212A</t>
+  </si>
+  <si>
+    <t>N00493469</t>
+  </si>
+  <si>
+    <t>GONZALES/CUMBIA VIVIANA</t>
+  </si>
+  <si>
+    <t>HUMA2505D</t>
+  </si>
+  <si>
+    <t>RESPONSABILIDAD SOCIAL</t>
+  </si>
+  <si>
+    <t>CON-WVHUMA2505D</t>
+  </si>
+  <si>
+    <t>N00513899</t>
+  </si>
+  <si>
+    <t>DAVILA/BANDA HECTOR DAVID</t>
+  </si>
+  <si>
+    <t>DERE1208D</t>
+  </si>
+  <si>
+    <t>DERECHO EMPRESARIAL Y LABORAL</t>
+  </si>
+  <si>
+    <t>CON-WVDERE1208D</t>
+  </si>
+  <si>
+    <t>N00538656</t>
+  </si>
+  <si>
+    <t>ALVARADO/VEGA LORENA</t>
+  </si>
+  <si>
+    <t>N00546820</t>
+  </si>
+  <si>
+    <t>CUELLAR/DE LA CRUZ MARIA CRISTINA</t>
+  </si>
+  <si>
+    <t>HUMA1111</t>
+  </si>
+  <si>
+    <t>ADM-WVHUMA1111</t>
+  </si>
+  <si>
+    <t>N00547189</t>
+  </si>
+  <si>
+    <t>NÚÑEZ/DIESTRA ADER FIORANE</t>
+  </si>
+  <si>
+    <t>ECON1209A</t>
+  </si>
+  <si>
+    <t>MICROECO. PARA ADMINISTRADORES</t>
+  </si>
+  <si>
+    <t>ADM-WVECON1209A</t>
+  </si>
+  <si>
+    <t>JULCA TORRES</t>
+  </si>
+  <si>
+    <t>GONZALES CUMBIA</t>
+  </si>
+  <si>
+    <t>DAVILA BANDA</t>
+  </si>
+  <si>
+    <t>ALVARADO VEGA</t>
+  </si>
+  <si>
+    <t>NÚÑEZ DIESTRA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CUELLAR DE LA CRUZ </t>
+  </si>
+  <si>
+    <t>HELEN DENISSE</t>
+  </si>
+  <si>
+    <t>HECTOR DAVID</t>
+  </si>
+  <si>
+    <t>ADER FIORANE</t>
+  </si>
+  <si>
+    <t>VIVIANA</t>
+  </si>
+  <si>
+    <t>LORENA</t>
+  </si>
+  <si>
+    <t>NEW</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -6284,16 +6400,36 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -6301,17 +6437,86 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color theme="5" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color theme="5" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -6652,7 +6857,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7204F3F-D373-4C60-8ECF-C0DF13D74D82}">
-  <dimension ref="A1:L673"/>
+  <dimension ref="A1:L679"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20.77734375" customWidth="1"/>
@@ -7681,7 +7886,7 @@
         <v>17</v>
       </c>
       <c r="I27" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="J27">
         <v>8</v>
@@ -32241,9 +32446,390 @@
         <v>2070</v>
       </c>
     </row>
+    <row r="674" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A674" t="s">
+        <v>2109</v>
+      </c>
+      <c r="B674" t="s">
+        <v>2103</v>
+      </c>
+      <c r="C674" t="s">
+        <v>2077</v>
+      </c>
+      <c r="D674" t="s">
+        <v>724</v>
+      </c>
+      <c r="E674" t="s">
+        <v>11</v>
+      </c>
+      <c r="F674" t="s">
+        <v>14</v>
+      </c>
+      <c r="G674" t="s">
+        <v>14</v>
+      </c>
+      <c r="H674" t="s">
+        <v>29</v>
+      </c>
+      <c r="I674" t="s">
+        <v>729</v>
+      </c>
+      <c r="J674">
+        <v>33</v>
+      </c>
+      <c r="K674" t="s">
+        <v>2114</v>
+      </c>
+    </row>
+    <row r="675" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A675" t="s">
+        <v>2112</v>
+      </c>
+      <c r="B675" t="s">
+        <v>2104</v>
+      </c>
+      <c r="C675" t="s">
+        <v>2082</v>
+      </c>
+      <c r="D675" t="s">
+        <v>724</v>
+      </c>
+      <c r="E675" t="s">
+        <v>11</v>
+      </c>
+      <c r="F675" t="s">
+        <v>14</v>
+      </c>
+      <c r="G675" t="s">
+        <v>14</v>
+      </c>
+      <c r="H675" t="s">
+        <v>12</v>
+      </c>
+      <c r="I675" t="s">
+        <v>729</v>
+      </c>
+      <c r="J675">
+        <v>43</v>
+      </c>
+      <c r="K675" t="s">
+        <v>2114</v>
+      </c>
+    </row>
+    <row r="676" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A676" t="s">
+        <v>2110</v>
+      </c>
+      <c r="B676" t="s">
+        <v>2105</v>
+      </c>
+      <c r="C676" t="s">
+        <v>2087</v>
+      </c>
+      <c r="D676" t="s">
+        <v>724</v>
+      </c>
+      <c r="E676" t="s">
+        <v>11</v>
+      </c>
+      <c r="F676" t="s">
+        <v>14</v>
+      </c>
+      <c r="G676" t="s">
+        <v>14</v>
+      </c>
+      <c r="H676" t="s">
+        <v>12</v>
+      </c>
+      <c r="I676" t="s">
+        <v>729</v>
+      </c>
+      <c r="J676">
+        <v>32</v>
+      </c>
+      <c r="K676" t="s">
+        <v>2114</v>
+      </c>
+    </row>
+    <row r="677" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A677" t="s">
+        <v>2113</v>
+      </c>
+      <c r="B677" t="s">
+        <v>2106</v>
+      </c>
+      <c r="C677" t="s">
+        <v>2092</v>
+      </c>
+      <c r="D677" t="s">
+        <v>724</v>
+      </c>
+      <c r="E677" t="s">
+        <v>11</v>
+      </c>
+      <c r="F677" t="s">
+        <v>14</v>
+      </c>
+      <c r="G677" t="s">
+        <v>14</v>
+      </c>
+      <c r="H677" t="s">
+        <v>29</v>
+      </c>
+      <c r="I677" t="s">
+        <v>729</v>
+      </c>
+      <c r="J677">
+        <v>7</v>
+      </c>
+      <c r="K677" t="s">
+        <v>2114</v>
+      </c>
+    </row>
+    <row r="678" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A678" t="s">
+        <v>1063</v>
+      </c>
+      <c r="B678" t="s">
+        <v>2108</v>
+      </c>
+      <c r="C678" t="s">
+        <v>2094</v>
+      </c>
+      <c r="D678" t="s">
+        <v>724</v>
+      </c>
+      <c r="E678" t="s">
+        <v>11</v>
+      </c>
+      <c r="F678" t="s">
+        <v>14</v>
+      </c>
+      <c r="G678" t="s">
+        <v>14</v>
+      </c>
+      <c r="H678" t="s">
+        <v>29</v>
+      </c>
+      <c r="I678" t="s">
+        <v>729</v>
+      </c>
+      <c r="J678">
+        <v>16</v>
+      </c>
+      <c r="K678" t="s">
+        <v>2114</v>
+      </c>
+    </row>
+    <row r="679" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A679" t="s">
+        <v>2111</v>
+      </c>
+      <c r="B679" t="s">
+        <v>2107</v>
+      </c>
+      <c r="C679" t="s">
+        <v>2098</v>
+      </c>
+      <c r="D679" t="s">
+        <v>724</v>
+      </c>
+      <c r="E679" t="s">
+        <v>11</v>
+      </c>
+      <c r="F679" t="s">
+        <v>14</v>
+      </c>
+      <c r="G679" t="s">
+        <v>14</v>
+      </c>
+      <c r="H679" t="s">
+        <v>29</v>
+      </c>
+      <c r="I679" t="s">
+        <v>729</v>
+      </c>
+      <c r="J679">
+        <v>20</v>
+      </c>
+      <c r="K679" t="s">
+        <v>2114</v>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:L679" xr:uid="{E7204F3F-D373-4C60-8ECF-C0DF13D74D82}"/>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D95C5153-5430-4FC6-95CA-413D7C02EAFC}">
+  <dimension ref="B2:I8"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="3.33203125" customWidth="1"/>
+    <col min="2" max="2" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="32.88671875" customWidth="1"/>
+    <col min="6" max="6" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="32" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.77734375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="3" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="3" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B3" s="1" t="s">
+        <v>2077</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>2078</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>2109</v>
+      </c>
+      <c r="E3" s="2"/>
+      <c r="F3" s="3" t="s">
+        <v>2079</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>2080</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>2081</v>
+      </c>
+      <c r="I3" s="5">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B4" s="1" t="s">
+        <v>2082</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>2083</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>2112</v>
+      </c>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2" t="s">
+        <v>2084</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>2085</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>2086</v>
+      </c>
+      <c r="I4" s="5">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B5" s="1" t="s">
+        <v>2087</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>2088</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>2110</v>
+      </c>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2" t="s">
+        <v>2089</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>2090</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>2091</v>
+      </c>
+      <c r="I5" s="5">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B6" s="1" t="s">
+        <v>2092</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>2093</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>2113</v>
+      </c>
+      <c r="E6" s="2"/>
+      <c r="F6" s="3" t="s">
+        <v>2079</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>2080</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>2081</v>
+      </c>
+      <c r="I6" s="5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B7" s="7" t="s">
+        <v>2094</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>2095</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>1063</v>
+      </c>
+      <c r="E7" s="8"/>
+      <c r="F7" s="9" t="s">
+        <v>2096</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>2085</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>2097</v>
+      </c>
+      <c r="I7" s="11">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B8" s="1" t="s">
+        <v>2098</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>2099</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>2111</v>
+      </c>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2" t="s">
+        <v>2100</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>2101</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>2102</v>
+      </c>
+      <c r="I8" s="5">
+        <v>20</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="F3:G8">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>AND(#REF!="No",#REF!="No")</formula>
+    </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
